--- a/artfynd/A 9401-2025 artfynd.xlsx
+++ b/artfynd/A 9401-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,77 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100180426</v>
+        <v>130818800</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>75318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Matt pricklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pachnolepia pruinata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+          <t>(Pers.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalkarlskärret bakom parkeringen, Upl</t>
+          <t>Dalkarskärret väst P-plats, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645243.8394889239</v>
+        <v>645187</v>
       </c>
       <c r="R2" t="n">
-        <v>6629300.835533998</v>
+        <v>6629325</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,57 +743,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mårten Vall</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mårten Vall</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115809896</v>
+        <v>81131989</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,45 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarskog, Upl</t>
+          <t>Dalkarlskärret, parkering, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645546</v>
+        <v>645162</v>
       </c>
       <c r="R3" t="n">
-        <v>6629030</v>
+        <v>6629331</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2019-12-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2019-12-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,18 +862,1055 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>77451269</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57194</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100114</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gråhakedopping</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Podiceps grisegena</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6629327</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jessica Ingman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jessica Ingman, Gunnar Lundström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77737459</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6629314</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>67960651</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>645167</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6629328</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-10-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>77451274</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6629327</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jessica Ingman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jessica Ingman, Gunnar Lundström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77737461</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>645170</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6629314</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-05-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Arne Wallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100275913</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>645169</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6629313</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100180426</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret bakom parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>645244</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6629301</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mårten Vall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mårten Vall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115809896</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hammarskog, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>645546</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6629030</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Björn Larsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Björn Larsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119738227</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalkarlskärret, Dalkarlskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>645186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6629325</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Christoffersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Christoffersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
